--- a/sample.xlsx
+++ b/sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\minmi\Documents\PythonAI\excel_utility\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04494AE6-7221-4BF8-B3CD-8F22CD851473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CFE07F-7412-4F23-9E2C-1960C38B2FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Hello</t>
   </si>
@@ -41,6 +41,10 @@
   </si>
   <si>
     <t>three</t>
+  </si>
+  <si>
+    <t>Hello</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -387,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
@@ -433,6 +437,9 @@
       <c r="A3">
         <v>30</v>
       </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
       <c r="D3" t="str">
         <f>IF(A4&gt;0,"positive","negative")</f>
         <v>negative</v>
@@ -484,6 +491,12 @@
       </c>
       <c r="F8">
         <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="D10">
+        <f t="array" ref="D10">SQRT(SUMSQ(IF(B1:B3="Hello",A1:A3)))</f>
+        <v>31.622776601683793</v>
       </c>
     </row>
   </sheetData>
